--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -1171,7 +1171,7 @@
         <v>98287455</v>
       </c>
       <c r="B6" t="n">
-        <v>57966</v>
+        <v>58021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>123391643</v>
       </c>
       <c r="B7" t="n">
-        <v>57966</v>
+        <v>58021</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>132276430</v>
       </c>
       <c r="B8" t="n">
-        <v>57988</v>
+        <v>58021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>123391631</v>
       </c>
       <c r="B11" t="n">
-        <v>57945</v>
+        <v>58000</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -1171,7 +1171,7 @@
         <v>98287455</v>
       </c>
       <c r="B6" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>123391643</v>
       </c>
       <c r="B7" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>132276430</v>
       </c>
       <c r="B8" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>123391631</v>
       </c>
       <c r="B11" t="n">
-        <v>58000</v>
+        <v>58013</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -1171,7 +1171,7 @@
         <v>98287455</v>
       </c>
       <c r="B6" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>123391643</v>
       </c>
       <c r="B7" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>132276430</v>
       </c>
       <c r="B8" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>123391631</v>
       </c>
       <c r="B11" t="n">
-        <v>58013</v>
+        <v>58015</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -1203,11 +1203,7 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Eriksdalsvägen, Sundsvall, Mpd</t>
@@ -1326,11 +1322,7 @@
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1450,11 +1442,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1812,11 +1800,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -1171,7 +1171,7 @@
         <v>98287455</v>
       </c>
       <c r="B6" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>123391643</v>
       </c>
       <c r="B7" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>132276430</v>
       </c>
       <c r="B8" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>123391631</v>
       </c>
       <c r="B11" t="n">
-        <v>58015</v>
+        <v>58025</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -1171,7 +1171,7 @@
         <v>98287455</v>
       </c>
       <c r="B6" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>123391643</v>
       </c>
       <c r="B7" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>132276430</v>
       </c>
       <c r="B8" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>123391631</v>
       </c>
       <c r="B11" t="n">
-        <v>58025</v>
+        <v>58026</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -1171,7 +1171,7 @@
         <v>98287455</v>
       </c>
       <c r="B6" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>123391643</v>
       </c>
       <c r="B7" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>132276430</v>
       </c>
       <c r="B8" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>123391631</v>
       </c>
       <c r="B11" t="n">
-        <v>58026</v>
+        <v>58027</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -1171,7 +1171,7 @@
         <v>98287455</v>
       </c>
       <c r="B6" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>123391643</v>
       </c>
       <c r="B7" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>132276430</v>
       </c>
       <c r="B8" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>123391631</v>
       </c>
       <c r="B11" t="n">
-        <v>58027</v>
+        <v>58030</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
